--- a/Data/EC/NIT-9008165173.xlsx
+++ b/Data/EC/NIT-9008165173.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABBA5724-34BB-4C31-BB02-E6A8B09AB55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE4FFA5-41C8-4787-9A77-6AE8B88535EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C248ADCD-9A05-4B33-85EB-098DB3D130E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B24F36F0-AA87-403A-A929-DC88A9A11022}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -821,22 +821,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA14F8DE-A829-887E-2D2E-82935EE83DB7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E824FC0-F8AF-A9CD-C7A1-360063268924}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -845,7 +845,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -858,7 +858,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1187,23 +1187,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B590C0C-BA37-4E32-A901-D26DCDEC2483}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D6687E7-08FE-483C-9A83-32D6C5D70B5F}">
   <dimension ref="B2:J246"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1216,7 +1216,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1227,7 +1227,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1238,7 +1238,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1249,8 +1249,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>129</v>
       </c>
@@ -1265,8 +1265,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1281,8 +1281,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>130</v>
       </c>
@@ -1297,8 +1297,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>131</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1392,7 +1392,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1415,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1438,7 +1438,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1461,7 +1461,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1484,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1599,7 +1599,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1668,7 +1668,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1714,7 +1714,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1737,7 +1737,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1829,7 +1829,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1852,7 +1852,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1875,7 +1875,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1898,7 +1898,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1944,7 +1944,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1967,7 +1967,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1990,7 +1990,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -2013,7 +2013,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2036,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -2059,7 +2059,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -2082,7 +2082,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2128,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2151,7 +2151,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2197,7 +2197,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2220,7 +2220,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2243,7 +2243,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2266,7 +2266,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2335,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2358,7 +2358,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2381,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2404,7 +2404,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2473,7 +2473,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2519,7 +2519,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2565,7 +2565,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2611,7 +2611,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2634,7 +2634,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2657,7 +2657,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2680,7 +2680,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2703,7 +2703,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2749,7 +2749,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2772,7 +2772,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2795,7 +2795,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2818,7 +2818,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2887,7 +2887,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +2910,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2933,7 +2933,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2979,7 +2979,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -3002,7 +3002,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -3048,7 +3048,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +3071,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -3094,7 +3094,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3117,7 +3117,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3140,7 +3140,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3186,7 +3186,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3209,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3232,7 +3232,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3255,7 +3255,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3278,7 +3278,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3301,7 +3301,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3324,7 +3324,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3370,7 +3370,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3393,7 +3393,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3416,7 +3416,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3439,7 +3439,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3462,7 +3462,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3508,7 +3508,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3531,7 +3531,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3554,7 +3554,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3577,7 +3577,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3600,7 +3600,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3669,7 +3669,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3692,7 +3692,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3715,7 +3715,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3761,7 +3761,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3784,7 +3784,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3807,7 +3807,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3830,7 +3830,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3853,7 +3853,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3876,7 +3876,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3922,7 +3922,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3945,7 +3945,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3968,7 +3968,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3991,7 +3991,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -4037,7 +4037,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -4060,7 +4060,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -4083,7 +4083,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -4129,7 +4129,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4152,7 +4152,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4175,7 +4175,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4198,7 +4198,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4221,7 +4221,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4244,7 +4244,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4267,7 +4267,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4290,7 +4290,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4336,7 +4336,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4359,7 +4359,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4405,7 +4405,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4428,7 +4428,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4451,7 +4451,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4474,7 +4474,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4497,7 +4497,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4520,7 +4520,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4543,7 +4543,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4566,7 +4566,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4589,7 +4589,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4612,7 +4612,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4635,7 +4635,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4658,7 +4658,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4681,7 +4681,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4704,7 +4704,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4727,7 +4727,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4750,7 +4750,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4773,7 +4773,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4796,7 +4796,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4819,7 +4819,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4842,7 +4842,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4865,7 +4865,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4888,7 +4888,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4911,7 +4911,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4934,7 +4934,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4957,7 +4957,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4980,7 +4980,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -5003,7 +5003,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -5026,7 +5026,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -5095,7 +5095,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -5118,7 +5118,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -5141,7 +5141,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5164,7 +5164,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5187,7 +5187,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5210,7 +5210,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5233,7 +5233,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5256,7 +5256,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5302,7 +5302,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5348,7 +5348,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5371,7 +5371,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5417,7 +5417,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5440,7 +5440,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5486,7 +5486,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5509,7 +5509,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5532,7 +5532,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5555,7 +5555,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5601,7 +5601,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5624,7 +5624,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5647,7 +5647,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5670,7 +5670,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5693,7 +5693,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5762,7 +5762,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5785,7 +5785,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5808,7 +5808,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5831,7 +5831,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5854,7 +5854,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5877,7 +5877,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5900,7 +5900,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5923,7 +5923,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5946,7 +5946,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5969,7 +5969,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5992,7 +5992,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -6015,7 +6015,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -6061,7 +6061,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -6084,7 +6084,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -6130,7 +6130,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -6153,7 +6153,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6176,7 +6176,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6199,7 +6199,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6222,7 +6222,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6245,7 +6245,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6268,7 +6268,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6291,7 +6291,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6314,7 +6314,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6360,7 +6360,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6383,7 +6383,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6406,7 +6406,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6429,7 +6429,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6452,7 +6452,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6475,7 +6475,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6498,7 +6498,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="21" t="s">
         <v>8</v>
       </c>
@@ -6521,7 +6521,7 @@
       <c r="I240" s="25"/>
       <c r="J240" s="26"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="32" t="s">
         <v>137</v>
       </c>
@@ -6532,7 +6532,7 @@
       <c r="I245" s="1"/>
       <c r="J245" s="1"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="32" t="s">
         <v>136</v>
       </c>
